--- a/data/trans_bre/P57_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 7,39</t>
+          <t>-6,5; 7,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 3,67</t>
+          <t>-18,6; 2,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 18,69</t>
+          <t>-14,56; 18,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 6,14</t>
+          <t>-25,98; 4,77</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,44</t>
+          <t>-3,46; 7,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 3,85</t>
+          <t>-25,7; 3,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 23,78</t>
+          <t>-9,58; 24,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 7,35</t>
+          <t>-46,06; 7,26</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 1,87</t>
+          <t>-8,18; 1,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 4,83</t>
+          <t>-6,79; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 6,01</t>
+          <t>-22,6; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 9,74</t>
+          <t>-12,26; 8,86</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 1,15</t>
+          <t>-9,32; 0,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,29; -7,38</t>
+          <t>-46,97; -6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 3,83</t>
+          <t>-32,09; 2,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,87; -16,45</t>
+          <t>-58,21; -14,92</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -0,63</t>
+          <t>-12,14; -0,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 0,86</t>
+          <t>-8,43; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,64; -2,44</t>
+          <t>-41,73; -1,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 2,79</t>
+          <t>-22,58; 4,62</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -1,23</t>
+          <t>-14,59; -2,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,12; -3,66</t>
+          <t>-32,6; -4,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,6; -5,23</t>
+          <t>-50,05; -9,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,38; -10,01</t>
+          <t>-77,56; -10,68</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 0,18</t>
+          <t>-12,03; 0,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,34; -1,54</t>
+          <t>-12,16; -1,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-53,79; 1,54</t>
+          <t>-53,51; 4,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-34,13; -5,73</t>
+          <t>-33,6; -5,54</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,2; -1,85</t>
+          <t>-6,38; -1,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -7,58</t>
+          <t>-23,38; -6,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -6,15</t>
+          <t>-20,02; -6,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,02; -16,0</t>
+          <t>-41,26; -13,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-7,84</t>
+          <t>-7,97</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-11,69%</t>
+          <t>-12,1%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 7,24</t>
+          <t>-6,88; 7,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 2,92</t>
+          <t>-18,62; 2,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 18,33</t>
+          <t>-14,53; 18,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 4,77</t>
+          <t>-25,74; 4,31</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-11,98%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 7,54</t>
+          <t>-2,78; 7,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 3,75</t>
+          <t>-6,65; 8,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 24,61</t>
+          <t>-7,98; 25,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,06; 7,26</t>
+          <t>-11,54; 17,76</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,04%</t>
+          <t>-0,43%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,86</t>
+          <t>-7,52; 2,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,29</t>
+          <t>-6,02; 5,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 6,29</t>
+          <t>-21,12; 8,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 8,86</t>
+          <t>-11,16; 11,54</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-23,4</t>
+          <t>-7,02</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-38,43%</t>
+          <t>-15,39%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 0,72</t>
+          <t>-9,2; 0,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,97; -6,6</t>
+          <t>-11,76; -2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 2,99</t>
+          <t>-31,32; 4,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -14,92</t>
+          <t>-24,26; -5,49</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-3,71</t>
+          <t>-3,82</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,53%</t>
+          <t>-10,8%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -0,32</t>
+          <t>-11,94; -0,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 1,49</t>
+          <t>-8,9; 1,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -1,33</t>
+          <t>-41,07; -2,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 4,62</t>
+          <t>-22,94; 3,67</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-17,27</t>
+          <t>-6,5</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-43,68%</t>
+          <t>-16,16%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -2,12</t>
+          <t>-14,16; -1,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,6; -4,0</t>
+          <t>-11,78; -1,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,05; -9,47</t>
+          <t>-51,57; -8,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-77,56; -10,68</t>
+          <t>-26,86; -3,09</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-7,13</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-21,3%</t>
+          <t>-21,81%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 0,56</t>
+          <t>-11,68; 0,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,16; -1,63</t>
+          <t>-12,84; -1,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-53,51; 4,04</t>
+          <t>-52,41; 6,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-33,6; -5,54</t>
+          <t>-34,92; -5,26</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-12,7</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-25,08%</t>
+          <t>-11,14%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -1,99</t>
+          <t>-6,08; -1,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,38; -6,57</t>
+          <t>-7,6; -2,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,02; -6,6</t>
+          <t>-19,39; -5,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,26; -13,9</t>
+          <t>-16,07; -6,13</t>
         </is>
       </c>
     </row>
